--- a/data/trans_orig/P19F$mañana-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016</t>
+          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016 (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>85935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119734</t>
+          <t>117752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>68620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95167</t>
+          <t>94004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166826</t>
+          <t>165790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206548</t>
+          <t>205417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>57327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88640</t>
+          <t>86786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76786</t>
+          <t>79008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119460</t>
+          <t>119251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156759</t>
+          <t>157916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168174</t>
+          <t>168483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>193366</t>
+          <t>193293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143963</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162522</t>
+          <t>161522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>318510</t>
+          <t>319797</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>349036</t>
+          <t>349955</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124020</t>
+          <t>124473</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159412</t>
+          <t>161434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98448</t>
+          <t>98786</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131789</t>
+          <t>129973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232202</t>
+          <t>231536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281552</t>
+          <t>279283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91086</t>
+          <t>88540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122953</t>
+          <t>124260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87680</t>
+          <t>88432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117521</t>
+          <t>118508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186536</t>
+          <t>186107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231022</t>
+          <t>231967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244214</t>
+          <t>241928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273086</t>
+          <t>271598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193469</t>
+          <t>194434</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220940</t>
+          <t>222339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>446427</t>
+          <t>445352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>486374</t>
+          <t>485025</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>113385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151003</t>
+          <t>148711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126778</t>
+          <t>128772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163191</t>
+          <t>165587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251679</t>
+          <t>252706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304412</t>
+          <t>302716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105975</t>
+          <t>104789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141916</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87623</t>
+          <t>89178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120432</t>
+          <t>120793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203883</t>
+          <t>202168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254722</t>
+          <t>253904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>259918</t>
+          <t>257593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>288197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>253526</t>
+          <t>253612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279962</t>
+          <t>281079</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>522516</t>
+          <t>519787</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562091</t>
+          <t>559874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111187</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150041</t>
+          <t>147756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143481</t>
+          <t>145684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180945</t>
+          <t>180846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265696</t>
+          <t>264807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316066</t>
+          <t>320150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99449</t>
+          <t>98174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136969</t>
+          <t>135146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85020</t>
+          <t>85241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>119815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196321</t>
+          <t>193769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244548</t>
+          <t>244439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>235280</t>
+          <t>234186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>268834</t>
+          <t>268305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>252047</t>
+          <t>251331</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>281421</t>
+          <t>280459</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>493841</t>
+          <t>494439</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>541030</t>
+          <t>540520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>86297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119069</t>
+          <t>119769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110553</t>
+          <t>111744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144867</t>
+          <t>144327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209789</t>
+          <t>208338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256725</t>
+          <t>256410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78633</t>
+          <t>78337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70610</t>
+          <t>70864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103334</t>
+          <t>102913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128135</t>
+          <t>130398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>173061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160013</t>
+          <t>161813</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>187246</t>
+          <t>189599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185454</t>
+          <t>188229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>215741</t>
+          <t>216794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>355807</t>
+          <t>356037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>395421</t>
+          <t>396736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53612</t>
+          <t>52015</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>78151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>72662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101537</t>
+          <t>101955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>133830</t>
+          <t>134656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171087</t>
+          <t>172603</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47188</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>57998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68028</t>
+          <t>67294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99551</t>
+          <t>100132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133948</t>
+          <t>134699</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154963</t>
+          <t>155273</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>140173</t>
+          <t>140206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>159866</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>282998</t>
+          <t>281828</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>310714</t>
+          <t>311183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63504</t>
+          <t>63031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78654</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99107</t>
+          <t>97204</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>133576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>65057</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>98646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83749</t>
+          <t>83861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101089</t>
+          <t>101472</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>140550</t>
+          <t>142485</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166704</t>
+          <t>167513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>234420</t>
+          <t>234167</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263728</t>
+          <t>264674</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>687665</t>
+          <t>678823</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>768305</t>
+          <t>766106</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>740774</t>
+          <t>740350</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>825126</t>
+          <t>828265</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1455044</t>
+          <t>1450680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1575069</t>
+          <t>1567574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>511174</t>
+          <t>508029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>586444</t>
+          <t>588603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>519259</t>
+          <t>522131</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>596831</t>
+          <t>603307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1042418</t>
+          <t>1046212</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1157740</t>
+          <t>1160166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1344079</t>
+          <t>1346408</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1415670</t>
+          <t>1417911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1374368</t>
+          <t>1369135</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1438597</t>
+          <t>1436644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2738106</t>
+          <t>2737006</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2840362</t>
+          <t>2840885</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85935</t>
+          <t>88807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117752</t>
+          <t>118659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68620</t>
+          <t>69450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94004</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165790</t>
+          <t>165022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205417</t>
+          <t>203982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57327</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86786</t>
+          <t>86504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53018</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79008</t>
+          <t>77755</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119251</t>
+          <t>117251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157916</t>
+          <t>156852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168483</t>
+          <t>168481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>193293</t>
+          <t>193901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144311</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161522</t>
+          <t>160917</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>319797</t>
+          <t>319508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>349955</t>
+          <t>349252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124473</t>
+          <t>122881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161434</t>
+          <t>158824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98786</t>
+          <t>98985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129973</t>
+          <t>130387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231536</t>
+          <t>231409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>279283</t>
+          <t>279120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88540</t>
+          <t>91058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124260</t>
+          <t>123787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88432</t>
+          <t>87602</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118508</t>
+          <t>117553</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186107</t>
+          <t>186246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231967</t>
+          <t>233608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241928</t>
+          <t>243374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>271598</t>
+          <t>273630</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194434</t>
+          <t>193881</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>222339</t>
+          <t>222548</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445352</t>
+          <t>447385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>485025</t>
+          <t>487151</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113385</t>
+          <t>114923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148711</t>
+          <t>150432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128772</t>
+          <t>125743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165587</t>
+          <t>161276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252706</t>
+          <t>252509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302716</t>
+          <t>303853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104789</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141886</t>
+          <t>144264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>88614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120793</t>
+          <t>121138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202168</t>
+          <t>200858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>253904</t>
+          <t>251910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>257593</t>
+          <t>258301</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288197</t>
+          <t>287880</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>253612</t>
+          <t>252813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>279598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519787</t>
+          <t>521557</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>559874</t>
+          <t>560205</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110423</t>
+          <t>109950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147756</t>
+          <t>149407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145684</t>
+          <t>144408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180846</t>
+          <t>180340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264807</t>
+          <t>264141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320150</t>
+          <t>319285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98174</t>
+          <t>98861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135146</t>
+          <t>134825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85241</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119815</t>
+          <t>118817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>193769</t>
+          <t>195496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244439</t>
+          <t>244564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>234186</t>
+          <t>234103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>268305</t>
+          <t>269466</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>251331</t>
+          <t>252107</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>280459</t>
+          <t>280434</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>494439</t>
+          <t>494811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>540520</t>
+          <t>538730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86297</t>
+          <t>87376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119769</t>
+          <t>119948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111744</t>
+          <t>109747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144327</t>
+          <t>144481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>208338</t>
+          <t>207985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256410</t>
+          <t>253618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>77575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70864</t>
+          <t>70954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102913</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130398</t>
+          <t>127449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173061</t>
+          <t>171402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161813</t>
+          <t>160026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>189599</t>
+          <t>188419</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>188229</t>
+          <t>185341</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216794</t>
+          <t>214058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356037</t>
+          <t>358984</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>396736</t>
+          <t>397021</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>53488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78151</t>
+          <t>78394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>73845</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101955</t>
+          <t>101504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134656</t>
+          <t>133979</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172603</t>
+          <t>170287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>48110</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57998</t>
+          <t>58120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67294</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>100170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134699</t>
+          <t>135455</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>155273</t>
+          <t>155049</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>140206</t>
+          <t>140592</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>159866</t>
+          <t>160689</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>281828</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>311183</t>
+          <t>310361</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63031</t>
+          <t>62364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78161</t>
+          <t>77828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97204</t>
+          <t>97941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133576</t>
+          <t>134565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67261</t>
+          <t>68521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65057</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98646</t>
+          <t>98061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83861</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101472</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142485</t>
+          <t>142516</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167513</t>
+          <t>167259</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>234167</t>
+          <t>232961</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>264674</t>
+          <t>263016</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>678823</t>
+          <t>688651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>766106</t>
+          <t>772357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>741817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>828265</t>
+          <t>827572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1450680</t>
+          <t>1450668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1567574</t>
+          <t>1565117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>508029</t>
+          <t>505745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>588603</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>522131</t>
+          <t>519547</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>603307</t>
+          <t>596318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1046212</t>
+          <t>1054609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1160166</t>
+          <t>1162218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1346408</t>
+          <t>1345093</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1417911</t>
+          <t>1415764</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1369135</t>
+          <t>1370750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1436644</t>
+          <t>1440189</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2737006</t>
+          <t>2738440</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2840885</t>
+          <t>2840308</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Edad-trans_orig.xlsx
@@ -828,112 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>172</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72107</t>
+          <t>181532</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>168481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86504</t>
+          <t>193901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>153870</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52672</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>160917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>136984</t>
+          <t>335402</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117251</t>
+          <t>319508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156852</t>
+          <t>349252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>181532</t>
+          <t>72107</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168481</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>193901</t>
+          <t>86504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153870</t>
+          <t>64877</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143014</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160917</t>
+          <t>77755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>136</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>335402</t>
+          <t>136984</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>319508</t>
+          <t>117251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>349252</t>
+          <t>156852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -1171,112 +1171,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>106256</t>
+          <t>258606</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91058</t>
+          <t>243374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123787</t>
+          <t>273630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>217</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>102399</t>
+          <t>208255</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87602</t>
+          <t>193881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117553</t>
+          <t>222548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>466</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>208655</t>
+          <t>466860</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186246</t>
+          <t>447385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>487151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -1284,112 +1284,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>258606</t>
+          <t>106256</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>243374</t>
+          <t>91058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273630</t>
+          <t>123787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>107</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>208255</t>
+          <t>102399</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193881</t>
+          <t>87602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>222548</t>
+          <t>117553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>466860</t>
+          <t>208655</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>447385</t>
+          <t>186246</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>487151</t>
+          <t>233608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -1514,112 +1514,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>260</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>124429</t>
+          <t>274397</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107061</t>
+          <t>258301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144264</t>
+          <t>287880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>267</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>104232</t>
+          <t>267125</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88614</t>
+          <t>252813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121138</t>
+          <t>279598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>527</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>228661</t>
+          <t>541522</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200858</t>
+          <t>521557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251910</t>
+          <t>560205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1627,112 +1627,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>274397</t>
+          <t>124429</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>258301</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>287880</t>
+          <t>144264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>267125</t>
+          <t>104232</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252813</t>
+          <t>88614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279598</t>
+          <t>121138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>541522</t>
+          <t>228661</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>521557</t>
+          <t>200858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>560205</t>
+          <t>251910</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -1857,112 +1857,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>116490</t>
+          <t>252703</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98861</t>
+          <t>234103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134825</t>
+          <t>269466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>249</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>101846</t>
+          <t>267387</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86228</t>
+          <t>252107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118817</t>
+          <t>280434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>483</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>218336</t>
+          <t>520090</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195496</t>
+          <t>494811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244564</t>
+          <t>538730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -1970,112 +1970,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252703</t>
+          <t>116490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>234103</t>
+          <t>98861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>269466</t>
+          <t>134825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>267387</t>
+          <t>101846</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>252107</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>280434</t>
+          <t>118817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>520090</t>
+          <t>218336</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>494811</t>
+          <t>195496</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>538730</t>
+          <t>244564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -2200,112 +2200,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>158</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>175758</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>160026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77575</t>
+          <t>188419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>180</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>86981</t>
+          <t>201978</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70954</t>
+          <t>185341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103785</t>
+          <t>214058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>338</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>150051</t>
+          <t>377736</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127449</t>
+          <t>358984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171402</t>
+          <t>397021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -2313,112 +2313,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>175758</t>
+          <t>63070</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160026</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188419</t>
+          <t>77575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>201978</t>
+          <t>86981</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185341</t>
+          <t>70954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214058</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>132</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>377736</t>
+          <t>150051</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>358984</t>
+          <t>127449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397021</t>
+          <t>171402</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -2543,112 +2543,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>142</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>146216</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>135455</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48110</t>
+          <t>155049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>142</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>46055</t>
+          <t>151060</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>140592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>160689</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>82518</t>
+          <t>297276</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66848</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100170</t>
+          <t>310361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -2656,112 +2656,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>146216</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135455</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>48110</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>151060</t>
+          <t>46055</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>140592</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160689</t>
+          <t>58120</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>297276</t>
+          <t>82518</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>310361</t>
+          <t>100170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -2886,112 +2886,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>93503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>52172</t>
+          <t>156182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39448</t>
+          <t>142516</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>68521</t>
+          <t>167259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>249685</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>232961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98061</t>
+          <t>263016</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -2999,112 +2999,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>93503</t>
+          <t>28769</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101836</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>156182</t>
+          <t>52172</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142516</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167259</t>
+          <t>68521</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>73</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>249685</t>
+          <t>80941</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>232961</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263016</t>
+          <t>98061</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -3229,112 +3229,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>547584</t>
+          <t>1382714</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>505745</t>
+          <t>1345093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>589137</t>
+          <t>1415764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>558561</t>
+          <t>1405857</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>519547</t>
+          <t>1370750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>596318</t>
+          <t>1440189</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1106145</t>
+          <t>2788572</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1054609</t>
+          <t>2738440</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1162218</t>
+          <t>2840308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -3342,112 +3342,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>521</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1382714</t>
+          <t>547584</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1345093</t>
+          <t>505745</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1415764</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>536</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1405857</t>
+          <t>558561</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1370750</t>
+          <t>519547</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1440189</t>
+          <t>596318</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2788572</t>
+          <t>1106145</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2738440</t>
+          <t>1054609</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2840308</t>
+          <t>1162218</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
